--- a/xlsx/그린바이오산업_특수분류표_4차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_4차.xlsx
@@ -199,7 +199,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오산업 특수분류 확정안 (제4차, 2026. 8. 30.)</t>
+          <t xml:space="preserve">그린바이오산업 특수분류 확정안 (제4차, 2026. 8. 31.)</t>
         </is>
       </c>
     </row>

--- a/xlsx/그린바이오산업_특수분류표_4차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_4차.xlsx
@@ -199,7 +199,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오산업 특수분류 확정안 (제4차, 2026. 8. 31.)</t>
+          <t xml:space="preserve">그린바이오산업 특수분류(안) (제4차, 2026. 8. 31.)</t>
         </is>
       </c>
     </row>
